--- a/FeederFlow.xlsx
+++ b/FeederFlow.xlsx
@@ -10,6 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BSD" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSD" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISD" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MISD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RVSD" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHSD" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNOSD" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1587,6 +1594,612 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ElemSchoolCode</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Elementary School</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MSSchoolCode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Middle School</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>HSSchoolCode</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="9" t="n">
+        <v>3104</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Echo Lake Elementary School</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Albert Einstein Middle School</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>3921</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Shorewood High School</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>3231</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Highland Terrace Elementary</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Albert Einstein Middle School</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3921</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Shorewood High School</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>3958</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Meridian Park Elementary School</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Albert Einstein Middle School</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3921</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Shorewood High School</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>3489</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Parkwood Elementary</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Albert Einstein Middle School</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>3921</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Shorewood High School</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>3527</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Melvin G Syre Elementary</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Albert Einstein Middle School</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>3921</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Shorewood High School</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>2990</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Briarcrest Elementary</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3387</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Kellogg Middle School</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3343</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Shorecrest High School</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>3230</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Brookside Elementary</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>3387</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Kellogg Middle School</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>3343</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Shorecrest High School</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>2185</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Lake Forest Park Elementary</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>3387</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Kellogg Middle School</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>3343</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Shorecrest High School</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>2703</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Ridgecrest Elementary</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>3387</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Kellogg Middle School</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>3343</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Shorecrest High School</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ElemSchoolCode</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Elementary School</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MSSchoolCode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Middle School</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>HSSchoolCode</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="9" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Cathcart Elementary</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>4145</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Valley View Middle School</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>5128</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Glacier Peak High School</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Little Cedars Elementary School</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>4145</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Valley View Middle School</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>5128</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Glacier Peak High School</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>4184</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Seattle Hill Elementary</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>4145</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Valley View Middle School</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>5128</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Glacier Peak High School</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>4383</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Totem Falls</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>4145</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Valley View Middle School</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>5128</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Glacier Peak High School</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>4366</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Cascade View Elementary</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>4395</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Centennial Middle School</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>2428</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Snohomish High School</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>3005</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Central Emerson Elementary</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>4395</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Centennial Middle School</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>2428</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Snohomish High School</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>4241</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Dutch Hill Elementary</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>4395</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Centennial Middle School</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>2428</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Snohomish High School</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>2073</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Machias Elementary</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>4395</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Centennial Middle School</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2428</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Snohomish High School</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>3561</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Riverview Elementary</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>4395</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Centennial Middle School</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2428</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Snohomish High School</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2589,7 +3202,7 @@
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Attendance boundary spans Bothell &amp; North Creek HS pathways — HS assignment depends on home address</t>
+          <t>Attendance boundary spans Bothell &amp; North Creek HS pathways; assignment depends on home address</t>
         </is>
       </c>
     </row>
@@ -2620,7 +3233,7 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Attendance boundary spans Bothell &amp; North Creek HS pathways — HS assignment depends on home address</t>
+          <t>Attendance boundary spans Bothell &amp; North Creek HS pathways; assignment depends on home address</t>
         </is>
       </c>
     </row>
@@ -2651,7 +3264,7 @@
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Attendance boundary spans North Creek &amp; Woodinville HS pathways — HS assignment depends on home address</t>
+          <t>Attendance boundary spans North Creek &amp; Woodinville HS pathways; assignment depends on home address</t>
         </is>
       </c>
     </row>
@@ -2744,7 +3357,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Ruby Bridges opened after 2017 — split geographically between Canyon Park MS and Skyview MS</t>
+          <t>Ruby Bridges opened after 2017; splits geographically between Canyon Park MS and Skyview MS</t>
         </is>
       </c>
     </row>
@@ -2775,7 +3388,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>Ruby Bridges opened after 2017 — split geographically between Canyon Park MS and Skyview MS</t>
+          <t>Ruby Bridges opened after 2017; splits geographically between Canyon Park MS and Skyview MS</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3471,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Bear Creek Elementary not found in OSPI 2024-25 data — may be too new or too small for public reporting</t>
+          <t>Bear Creek Elementary not found in OSPI 2024-25 data; may be too new or too small for public reporting</t>
         </is>
       </c>
     </row>
@@ -2970,7 +3583,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>Attendance boundary spans North Creek &amp; Woodinville HS pathways — HS assignment depends on home address</t>
+          <t>Attendance boundary spans North Creek &amp; Woodinville HS pathways; assignment depends on home address</t>
         </is>
       </c>
     </row>
@@ -3509,4 +4122,3950 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ElemSchoolCode</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Elementary School</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MSSchoolCode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Middle School</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>HSSchoolCode</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="9" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Beverly Elementary</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>3353</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Meadowdale Middle School</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>3464</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Meadowdale High School</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>3122</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Lynndale Elementary</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>3353</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Meadowdale Middle School</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3464</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Meadowdale High School</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Meadowdale Elementary</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>3353</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Meadowdale Middle School</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3464</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Meadowdale High School</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>3461</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Seaview Elementary</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>3353</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Meadowdale Middle School</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>3464</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Meadowdale High School</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>3410</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Spruce Elementary</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3353</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Meadowdale Middle School</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>3464</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Meadowdale High School</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>3606</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Edmonds Elementary</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3353</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Meadowdale Middle School</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3464</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Meadowdale High School</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Edmonds Elementary is split geographically; a portion feeds into College Place Middle / Edmonds-Woodway High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>3606</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Edmonds Elementary</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>3754</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>College Place Middle School</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>3123</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Edmonds Woodway High School</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Edmonds Elementary is split geographically; a portion feeds into College Place Middle / Edmonds-Woodway High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>3409</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Cedar Valley Elementary</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>3755</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Lynnwood High School</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Lynnwood Elementary</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>3755</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Lynnwood High School</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2887</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Martha Lake Elementary</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>3755</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Lynnwood High School</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>3608</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Oak Heights Elementary</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>3755</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Lynnwood High School</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>3607</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Hazelwood Elementary</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>3303</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace High School</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Hazelwood Elementary feeds to Alderwood Middle, then either Mountlake Terrace High or Lynnwood High depending on address</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="n">
+        <v>3607</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Hazelwood Elementary</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>3755</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Lynnwood High School</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Hazelwood Elementary feeds to Alderwood Middle, then either Mountlake Terrace High or Lynnwood High depending on address</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>3689</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>3303</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace High School</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary is split: feeds Alderwood MS or Brier Terrace MS, then Mountlake Terrace High or Lynnwood High depending on address</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="9" t="n">
+        <v>3689</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>3560</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Alderwood Middle School</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>3755</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Lynnwood High School</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary is split: feeds Alderwood MS or Brier Terrace MS, then Mountlake Terrace High or Lynnwood High depending on address</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>3689</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Brier Terrace Middle School</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>3303</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace High School</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary is split: feeds Alderwood MS or Brier Terrace MS, then Mountlake Terrace High or Lynnwood High depending on address</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>3689</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Brier Terrace Middle School</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>3755</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Lynnwood High School</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Hilltop Elementary is split: feeds Alderwood MS or Brier Terrace MS, then Mountlake Terrace High or Lynnwood High depending on address</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>3536</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Brier Elementary</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Brier Terrace Middle School</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>3303</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace High School</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="9" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Cedar Way Elementary</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Brier Terrace Middle School</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>3303</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace High School</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>3254</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace Elementary</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Brier Terrace Middle School</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>3303</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace High School</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="9" t="n">
+        <v>2888</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Terrace Park Elementary</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Brier Terrace Middle School</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>3303</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Mountlake Terrace High School</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>3691</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>College Place Elementary</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>3754</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>College Place Middle School</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>3123</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Edmonds Woodway High School</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="9" t="n">
+        <v>3605</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Sherwood Elementary</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>3754</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>College Place Middle School</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>3123</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>Edmonds Woodway High School</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>3186</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Westgate Elementary</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>3754</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>College Place Middle School</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>3123</v>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>Edmonds Woodway High School</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ElemSchoolCode</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Elementary School</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MSSchoolCode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Middle School</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>HSSchoolCode</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="9" t="n">
+        <v>2065</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Garfield Elementary School</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>2364</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>North Middle School</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>2883</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Hawthorne Elementary School</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>2364</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>North Middle School</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>2751</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Jackson Elementary School</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>2364</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>North Middle School</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>2752</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Whittier Elementary</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>2364</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>North Middle School</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>3184</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Emerson Elementary School</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>3184</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Emerson Elementary School</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>2811</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Lowell Elementary</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>2811</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Lowell Elementary</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>2669</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Madison Elementary</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2669</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Madison Elementary</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>3002</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>View Ridge Elementary</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>3002</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>View Ridge Elementary</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>3253</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Evergreen Middle School</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Evergreen MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="n">
+        <v>3686</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Monroe Elementary</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Eisenhower MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>3686</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Monroe Elementary</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Eisenhower MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="9" t="n">
+        <v>3533</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Jefferson Elementary</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Eisenhower MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>3533</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Jefferson Elementary</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Eisenhower MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>2545</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Silver Lake Elementary</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Silver Lake splits across multiple middle schools by address; Eisenhower MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>2545</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Silver Lake Elementary</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Silver Lake splits across multiple middle schools by address; Eisenhower MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="9" t="n">
+        <v>2545</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Silver Lake Elementary</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>4334</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Heatherwood Middle School</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Silver Lake splits across multiple middle schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>5091</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Forest View Elementary School</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Gateway MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="9" t="n">
+        <v>5091</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Forest View Elementary School</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Gateway MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>4298</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Silver Firs Elementary</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Gateway MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="9" t="n">
+        <v>4298</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Silver Firs Elementary</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Gateway MS splits across multiple high schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>5570</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Tambark Creek Elementary School</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Tambark Creek splits across multiple middle schools by address; Gateway MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="9" t="n">
+        <v>5570</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Tambark Creek Elementary School</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Tambark Creek splits across multiple middle schools by address; Gateway MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>5570</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Tambark Creek Elementary School</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>4334</v>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Heatherwood Middle School</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Tambark Creek splits across multiple middle schools by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="9" t="n">
+        <v>4530</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Penny Creek Elementary</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Penny Creek splits across multiple middle schools by address; Gateway MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>4530</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Penny Creek Elementary</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>4437</v>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Gateway Middle School</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Penny Creek splits across multiple middle schools by address; Gateway MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="9" t="n">
+        <v>4530</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Penny Creek Elementary</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Cascade High School</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Penny Creek splits across multiple middle schools by address; Eisenhower MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>4530</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Penny Creek Elementary</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Eisenhower Middle School</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>Everett High School</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Penny Creek splits across multiple middle schools by address; Eisenhower MS splits across multiple high schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="9" t="n">
+        <v>4382</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Cedar Wood Elementary</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>4334</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Heatherwood Middle School</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>4316</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Mill Creek Elementary</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>4334</v>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Heatherwood Middle School</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>4125</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Woodside Elementary</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>4334</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Heatherwood Middle School</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>4438</v>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>Henry M. Jackson High School</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ElemSchoolCode</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Elementary School</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MSSchoolCode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Middle School</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>HSSchoolCode</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="9" t="n">
+        <v>3162</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Island Park Elementary</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Islander Middle School</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Mercer Island High School</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>2981</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Lakeridge Elementary School</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Islander Middle School</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Mercer Island High School</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Northwood Elementary School</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Islander Middle School</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Mercer Island High School</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>3433</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>West Mercer Elementary</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Islander Middle School</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Mercer Island High School</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ElemSchoolCode</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Elementary School</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MSSchoolCode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Middle School</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>HSSchoolCode</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="9" t="n">
+        <v>2209</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Broadview-Thomson K-8 School</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>5486</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Robert Eagle Staff Middle School</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>3276</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Ingraham High School</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>2977</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Viewlands Elementary School</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>5486</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Robert Eagle Staff Middle School</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3276</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Ingraham High School</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>2256</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Olympic View Elementary School</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>5486</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Robert Eagle Staff Middle School</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3276</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Ingraham High School</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>5292</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Cascadia Elementary</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>5486</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Robert Eagle Staff Middle School</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>3276</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Ingraham High School</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>2462</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Loyal Heights Elementary School</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3277</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Whitman Middle School</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>2220</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Ballard High School</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>2138</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Adams Elementary School</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3277</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Whitman Middle School</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>2220</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Ballard High School</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>2092</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Whittier Elementary School</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>3277</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Whitman Middle School</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>2220</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Ballard High School</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>North Beach Elementary School</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>3277</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Whitman Middle School</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2220</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Ballard High School</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>2976</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Olympic Hills Elementary School</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>5351</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Jane Addams Middle School</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>3479</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Nathan Hale High School</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>5487</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Cedar Park Elementary School</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>5351</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Jane Addams Middle School</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>3479</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Nathan Hale High School</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>5175</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Hazel Wolf K-8</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>5351</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Jane Addams Middle School</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>3479</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Nathan Hale High School</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>2975</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>John Rogers Elementary School</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>5351</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Jane Addams Middle School</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>3479</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Nathan Hale High School</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="n">
+        <v>3028</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Sacajawea Elementary School</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>5351</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Jane Addams Middle School</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>3479</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Nathan Hale High School</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>3026</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Wedgwood Elementary School</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Eckstein Middle School</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>2285</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Roosevelt High School</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="9" t="n">
+        <v>2667</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>View Ridge Elementary School</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Eckstein Middle School</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>2285</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Roosevelt High School</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Sand Point Elementary</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Eckstein Middle School</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>2285</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Roosevelt High School</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>2372</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Bryant Elementary School</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Eckstein Middle School</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>2285</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Roosevelt High School</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>2437</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Laurelhurst Elementary School</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Eckstein Middle School</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>2285</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Roosevelt High School</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="9" t="n">
+        <v>5488</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Stephen Decatur Elementary School</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>2729</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Eckstein Middle School</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>2285</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>Roosevelt High School</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>2123</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Greenwood Elementary School</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>2371</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Hamilton International Middle School</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="9" t="n">
+        <v>2450</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Daniel Bagley Elementary School</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>2371</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Hamilton International Middle School</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>2142</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>West Woodland Elementary School</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>2371</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Hamilton International Middle School</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="9" t="n">
+        <v>5203</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>McDonald International School</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>2371</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Hamilton International Middle School</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>2061</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Green Lake Elementary School</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>2371</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Hamilton International Middle School</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="9" t="n">
+        <v>2081</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>John Stanford International School</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2371</v>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Hamilton International Middle School</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>3717</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>B F Day Elementary School</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>2371</v>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Hamilton International Middle School</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="9" t="n">
+        <v>2838</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Catharine Blaine K-8 School</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>McClure Middle School</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>5565</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Magnolia Elementary School</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>McClure Middle School</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="9" t="n">
+        <v>2183</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Lawton Elementary School</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>McClure Middle School</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>2090</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Frantz Coe Elementary School</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>McClure Middle School</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="9" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Queen Anne Elementary</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>McClure Middle School</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>2063</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>John Hay Elementary School</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>McClure Middle School</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>5566</v>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln High School</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>2322</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Montlake Elementary School</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Edmonds S. Meany Middle School</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Stevens Elementary School</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Edmonds S. Meany Middle School</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>2201</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>McGilvra Elementary School</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Edmonds S. Meany Middle School</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>3714</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Lowell Elementary School</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Edmonds S. Meany Middle School</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="9" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Madrona K-5 School</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>4064</v>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Washington Middle School</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="9" t="n">
+        <v>2307</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Bailey Gatzert Elementary School</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>4064</v>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Washington Middle School</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="9" t="n">
+        <v>2121</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Leschi Elementary School</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>4064</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Washington Middle School</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="9" t="n">
+        <v>2141</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Thurgood Marshall Elementary</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>4064</v>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Washington Middle School</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>Garfield High School</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="9" t="n">
+        <v>2070</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Beacon Hill International School</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Mercer International Middle School</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>2182</v>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Franklin High School</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="9" t="n">
+        <v>3478</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Kimball Elementary School</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>Mercer International Middle School</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>2182</v>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>Franklin High School</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="9" t="n">
+        <v>2143</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>John Muir Elementary School</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Mercer International Middle School</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>2182</v>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>Franklin High School</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="9" t="n">
+        <v>2353</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Maple Elementary School</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Mercer International Middle School</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>2182</v>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>Franklin High School</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="9" t="n">
+        <v>4248</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Hawthorne Elementary School</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Mercer International Middle School</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>2182</v>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>Franklin High School</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="9" t="n">
+        <v>3803</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Dearborn Park International School</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>Mercer International Middle School</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>2182</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>Franklin High School</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="9" t="n">
+        <v>2733</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Lafayette Elementary School</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Madison Middle School</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>West Seattle High School</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="9" t="n">
+        <v>3429</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Genesee Hill Elementary</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Madison Middle School</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>West Seattle High School</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="9" t="n">
+        <v>3518</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Fairmount Park Elementary School</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Madison Middle School</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>West Seattle High School</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="9" t="n">
+        <v>2181</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Alki Elementary School</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>Madison Middle School</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>West Seattle High School</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="9" t="n">
+        <v>2645</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>West Seattle Elementary School</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Madison Middle School</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>West Seattle High School</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="9" t="n">
+        <v>5276</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Louisa Boren STEM K-8</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>Madison Middle School</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>West Seattle High School</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="inlineStr"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="9" t="n">
+        <v>3665</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Sanislo Elementary School</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>2839</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>David T. Denny International Middle School</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>3096</v>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>Chief Sealth International High School</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="9" t="n">
+        <v>2139</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Gatewood Elementary School</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>2839</v>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>David T. Denny International Middle School</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>3096</v>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>Chief Sealth International High School</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="9" t="n">
+        <v>3157</v>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Roxhill Elementary School</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>2839</v>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>David T. Denny International Middle School</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>3096</v>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>Chief Sealth International High School</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="9" t="n">
+        <v>2730</v>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Arbor Heights Elementary School</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>2839</v>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>David T. Denny International Middle School</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>3096</v>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>Chief Sealth International High School</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="9" t="n">
+        <v>2269</v>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Highland Park Elementary School</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>2839</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>David T. Denny International Middle School</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>3096</v>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>Chief Sealth International High School</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="9" t="n">
+        <v>2199</v>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Concord International School</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>2839</v>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>David T. Denny International Middle School</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>3096</v>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>Chief Sealth International High School</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="9" t="n">
+        <v>2120</v>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Rising Star Elementary School</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="9" t="n">
+        <v>3581</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Wing Luke Elementary School</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="9" t="n">
+        <v>2089</v>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Martin Luther King Jr. Elementary School</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="9" t="n">
+        <v>3378</v>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Graham Hill Elementary School</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="9" t="n">
+        <v>2321</v>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Dunlap Elementary School</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="9" t="n">
+        <v>4218</v>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>South Shore PK-8 School</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="inlineStr"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="9" t="n">
+        <v>2118</v>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Emerson Elementary School</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="inlineStr"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="9" t="n">
+        <v>3380</v>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Rainier View Elementary School</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>3774</v>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Aki Kurose Middle School</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>3327</v>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>Rainier Beach High School</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ElemSchoolCode</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Elementary School</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MSSchoolCode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Middle School</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>HSSchoolCode</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="9" t="n">
+        <v>2485</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Carnation Elementary School</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>4318</v>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Tolt Middle School</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>3524</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Cedarcrest High School</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Cherry Valley Elementary School</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>4318</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Tolt Middle School</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3524</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Cedarcrest High School</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>4332</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Stillwater Elementary</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>4318</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Tolt Middle School</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3524</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Cedarcrest High School</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>